--- a/datos/03-fab_queso_sim.xlsx
+++ b/datos/03-fab_queso_sim.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="337" documentId="8_{CF1E59C1-CA92-4C88-887C-A78A793F0426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A2E1E21-D668-4866-9DB4-7A5497C9AAF8}"/>
+  <xr:revisionPtr revIDLastSave="339" documentId="8_{CF1E59C1-CA92-4C88-887C-A78A793F0426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A7F8342-7135-4BFC-AE29-00A108EEAECC}"/>
   <bookViews>
-    <workbookView xWindow="7500" yWindow="1200" windowWidth="23595" windowHeight="14250" activeTab="2" xr2:uid="{3820C6B5-2803-4858-AF88-A2FCB3D2881D}"/>
+    <workbookView xWindow="2820" yWindow="540" windowWidth="23595" windowHeight="14250" activeTab="4" xr2:uid="{3820C6B5-2803-4858-AF88-A2FCB3D2881D}"/>
   </bookViews>
   <sheets>
     <sheet name="fab_queso_sim" sheetId="1" r:id="rId1"/>
@@ -909,75 +909,6 @@
   </cellStyles>
   <dxfs count="39">
     <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="164" formatCode="0.0%"/>
     </dxf>
     <dxf>
@@ -1096,6 +1027,75 @@
     </dxf>
     <dxf>
       <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
@@ -12118,7 +12118,7 @@
     <dataField name="Desviación_x000a_total_x000a_(%)" fld="31" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="13">
+    <format dxfId="29">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -12130,7 +12130,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="12">
+    <format dxfId="28">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -12142,7 +12142,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="11">
+    <format dxfId="27">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -12154,13 +12154,13 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="10">
+    <format dxfId="26">
       <pivotArea field="22" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="25">
       <pivotArea field="22" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="24">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12169,7 +12169,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="7">
+    <format dxfId="23">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12178,7 +12178,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="6">
+    <format dxfId="22">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12187,7 +12187,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="5">
+    <format dxfId="21">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12196,7 +12196,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="4">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12205,7 +12205,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="3">
+    <format dxfId="19">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12214,7 +12214,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="2">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12223,7 +12223,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="1">
+    <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12232,7 +12232,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12797,13 +12797,13 @@
     <dataField name="Coef recup MP/ESM" fld="39" baseField="20" baseItem="9" numFmtId="164"/>
   </dataFields>
   <formats count="16">
-    <format dxfId="38">
+    <format dxfId="15">
       <pivotArea field="22" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="37">
+    <format dxfId="14">
       <pivotArea field="22" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="36">
+    <format dxfId="13">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12812,7 +12812,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="35">
+    <format dxfId="12">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12821,7 +12821,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="34">
+    <format dxfId="11">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12830,7 +12830,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="33">
+    <format dxfId="10">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12839,7 +12839,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="32">
+    <format dxfId="9">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12848,7 +12848,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="31">
+    <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12857,7 +12857,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="30">
+    <format dxfId="7">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12866,7 +12866,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="29">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12875,7 +12875,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="28">
+    <format dxfId="5">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12884,7 +12884,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="27">
+    <format dxfId="4">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12893,7 +12893,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="26">
+    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12902,7 +12902,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="2">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12911,7 +12911,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="24">
+    <format dxfId="1">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12920,7 +12920,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="23">
+    <format dxfId="0">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -13633,7 +13633,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4EAA836B-7E28-4F5F-B497-A3F78E114EA5}" name="Tabla2" displayName="Tabla2" ref="A1:T365" totalsRowShown="0">
   <autoFilter ref="A1:T365" xr:uid="{4EAA836B-7E28-4F5F-B497-A3F78E114EA5}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{0EAAFB95-0462-4A46-895E-2C8949E731AE}" name="fecha" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{0EAAFB95-0462-4A46-895E-2C8949E731AE}" name="fecha" dataDxfId="38"/>
     <tableColumn id="2" xr3:uid="{B99A55EC-062A-41A1-9987-66C4A77606BA}" name="entrada_kg"/>
     <tableColumn id="3" xr3:uid="{DA11BF6E-5AFF-4E5A-A825-C843AA73522C}" name="entrada_litros"/>
     <tableColumn id="4" xr3:uid="{ED230348-1BB5-43D8-ADE4-81312B15A5A9}" name="entrada_grasa_g_l"/>
@@ -13645,28 +13645,28 @@
     <tableColumn id="10" xr3:uid="{E2106BDF-6A85-4EF5-B55C-0D7CFEBF9BD8}" name="queso_kg"/>
     <tableColumn id="11" xr3:uid="{8A9920A8-F994-40CF-861E-A78626F5DFA0}" name="queso_est_pct"/>
     <tableColumn id="12" xr3:uid="{7BEF460E-C8FD-436F-A522-912A1E3FC0C1}" name="queso_mg_pct"/>
-    <tableColumn id="13" xr3:uid="{4C6E2762-B054-43B2-9A21-BCBED25CD3AE}" name="entrada_grasa_kg" dataDxfId="21">
+    <tableColumn id="13" xr3:uid="{4C6E2762-B054-43B2-9A21-BCBED25CD3AE}" name="entrada_grasa_kg" dataDxfId="37">
       <calculatedColumnFormula>Tabla2[[#This Row],[entrada_litros]]*Tabla2[[#This Row],[entrada_grasa_g_l]]/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{72F3B23C-8C52-4610-8DE2-F2CFF573C1A3}" name="entrada_prot_kg" dataDxfId="20">
+    <tableColumn id="14" xr3:uid="{72F3B23C-8C52-4610-8DE2-F2CFF573C1A3}" name="entrada_prot_kg" dataDxfId="36">
       <calculatedColumnFormula>Tabla2[[#This Row],[entrada_litros]]*Tabla2[[#This Row],[entrada_prot_g_l]]/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{1F2FDCA1-AA37-432A-9889-51F7AB1D868E}" name="cuba_fab_grasa_kg" dataDxfId="19">
+    <tableColumn id="15" xr3:uid="{1F2FDCA1-AA37-432A-9889-51F7AB1D868E}" name="cuba_fab_grasa_kg" dataDxfId="35">
       <calculatedColumnFormula>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_grasa_g_l]]/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{5C5A0D35-AC30-4575-AD36-DFD4AB1AAE78}" name="cuba_fab_prot_kg" dataDxfId="18">
+    <tableColumn id="16" xr3:uid="{5C5A0D35-AC30-4575-AD36-DFD4AB1AAE78}" name="cuba_fab_prot_kg" dataDxfId="34">
       <calculatedColumnFormula>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{60870160-690E-43AA-BA91-2F2A23C024EA}" name="queso_est_kg" dataDxfId="17">
+    <tableColumn id="20" xr3:uid="{60870160-690E-43AA-BA91-2F2A23C024EA}" name="queso_est_kg" dataDxfId="33">
       <calculatedColumnFormula>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{4D671BF4-2751-4C20-94DC-8DF5C5BD43DC}" name="queso_mg_kg" dataDxfId="16">
+    <tableColumn id="19" xr3:uid="{4D671BF4-2751-4C20-94DC-8DF5C5BD43DC}" name="queso_mg_kg" dataDxfId="32">
       <calculatedColumnFormula>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_mg_pct]]/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{557AB84E-05A8-425D-881C-BCA8985A6A4E}" name="semanaISO" dataDxfId="15">
+    <tableColumn id="17" xr3:uid="{557AB84E-05A8-425D-881C-BCA8985A6A4E}" name="semanaISO" dataDxfId="31">
       <calculatedColumnFormula>_xlfn.ISOWEEKNUM(Tabla2[[#This Row],[fecha]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{4C92060C-D738-42A2-A8B9-D53895DE3195}" name="semana" dataDxfId="14"/>
+    <tableColumn id="18" xr3:uid="{4C92060C-D738-42A2-A8B9-D53895DE3195}" name="semana" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
